--- a/data/trans_bre/P19-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 12,93</t>
+          <t>3,43; 12,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,92</t>
+          <t>2,52; 12,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 10,65</t>
+          <t>0,68; 11,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 11,36</t>
+          <t>1,61; 11,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 63,91</t>
+          <t>13,18; 60,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 58,56</t>
+          <t>9,94; 61,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 40,31</t>
+          <t>1,87; 41,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 58,17</t>
+          <t>5,7; 60,04</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 10,8</t>
+          <t>2,27; 10,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,88</t>
+          <t>2,6; 10,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,4</t>
+          <t>3,17; 11,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 17,3</t>
+          <t>1,74; 17,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 45,99</t>
+          <t>8,11; 46,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 50,06</t>
+          <t>10,17; 48,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,06; 42,91</t>
+          <t>9,57; 45,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 149,34</t>
+          <t>6,47; 158,75</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 10,32</t>
+          <t>-0,18; 10,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 7,65</t>
+          <t>-1,85; 7,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,04</t>
+          <t>-0,81; 8,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 7,88</t>
+          <t>-17,77; 8,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 41,13</t>
+          <t>-0,94; 40,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 31,6</t>
+          <t>-6,51; 33,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 31,7</t>
+          <t>-1,96; 29,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 25,3</t>
+          <t>-53,03; 28,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,02</t>
+          <t>2,02; 10,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,71</t>
+          <t>1,46; 10,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 8,45</t>
+          <t>0,31; 8,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 8,15</t>
+          <t>-2,8; 8,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 43,43</t>
+          <t>7,31; 45,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 40,23</t>
+          <t>5,09; 42,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 31,81</t>
+          <t>0,94; 32,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 30,38</t>
+          <t>-8,07; 31,34</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,56</t>
+          <t>4,29; 8,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,05</t>
+          <t>3,26; 7,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,84</t>
+          <t>3,2; 7,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,45</t>
+          <t>-0,29; 10,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,09; 35,84</t>
+          <t>16,31; 36,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,85; 34,15</t>
+          <t>12,91; 32,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 28,27</t>
+          <t>10,67; 27,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 49,22</t>
+          <t>-0,46; 46,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,59</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 12,91</t>
+          <t>3,47; 12,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 12,04</t>
+          <t>2,56; 12,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 11,0</t>
+          <t>0,87; 10,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,72</t>
+          <t>2,42; 11,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,18; 60,07</t>
+          <t>14,29; 63,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 61,35</t>
+          <t>10,12; 63,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 41,92</t>
+          <t>2,85; 42,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 60,04</t>
+          <t>9,74; 56,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,28</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,6</t>
+          <t>2,18; 10,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,47</t>
+          <t>2,41; 10,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 11,75</t>
+          <t>2,91; 11,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 17,25</t>
+          <t>-0,72; 7,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 46,88</t>
+          <t>8,1; 46,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 48,67</t>
+          <t>9,53; 48,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 45,36</t>
+          <t>9,23; 44,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 158,75</t>
+          <t>-2,71; 33,8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-9,06%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 10,2</t>
+          <t>0,25; 10,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,81</t>
+          <t>-1,96; 7,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 8,48</t>
+          <t>-0,55; 8,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 8,78</t>
+          <t>-1,23; 8,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 40,95</t>
+          <t>0,34; 40,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 33,16</t>
+          <t>-7,13; 32,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 29,77</t>
+          <t>-1,65; 30,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 28,21</t>
+          <t>-3,69; 32,49</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,14</t>
+          <t>2,07; 10,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 10,03</t>
+          <t>2,16; 9,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 8,72</t>
+          <t>-0,13; 8,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 8,33</t>
+          <t>1,52; 9,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 45,17</t>
+          <t>7,52; 44,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 42,04</t>
+          <t>7,51; 41,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 32,39</t>
+          <t>-0,32; 31,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 31,34</t>
+          <t>4,94; 38,36</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,66</t>
+          <t>4,14; 8,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,68</t>
+          <t>3,25; 7,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,71</t>
+          <t>3,11; 7,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,18</t>
+          <t>2,68; 6,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 36,05</t>
+          <t>15,76; 35,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,91; 32,61</t>
+          <t>12,91; 32,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,67; 27,87</t>
+          <t>10,24; 28,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 46,89</t>
+          <t>9,66; 28,26</t>
         </is>
       </c>
     </row>
